--- a/data/rateBuildUp/File1/RPT_RPT2570073654838NR_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT2570073654838NR_rateBuildUp.xlsx
@@ -14308,19 +14308,19 @@
         </is>
       </c>
       <c r="C61" s="187" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="D61" s="179" t="n">
         <v>0.0</v>
       </c>
       <c r="E61" s="179" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="F61" s="179" t="n">
         <v>0.0</v>
       </c>
       <c r="G61" s="202" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="H61" s="187" t="n">
         <v>8417.608252999977</v>
@@ -14358,19 +14358,19 @@
         </is>
       </c>
       <c r="T61" s="203" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="U61" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="V61" s="204" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="W61" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="X61" s="205" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="Y61" s="203" t="n">
         <v>8417.608252999977</v>
@@ -16343,34 +16343,34 @@
         </is>
       </c>
       <c r="C70" s="226" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="D70" s="227" t="n">
         <v>0.0</v>
       </c>
       <c r="E70" s="227" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="F70" s="227" t="n">
         <v>0.0</v>
       </c>
       <c r="G70" s="243" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="H70" s="189" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="I70" s="190" t="n">
         <v>0.0</v>
       </c>
       <c r="J70" s="190" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="K70" s="190" t="n">
         <v>0.0</v>
       </c>
       <c r="L70" s="244" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="M70" s="190" t="n">
         <v>8417.608252999977</v>
@@ -16393,34 +16393,34 @@
         </is>
       </c>
       <c r="T70" s="245" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="U70" s="246" t="n">
         <v>0.0</v>
       </c>
       <c r="V70" s="246" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="W70" s="246" t="n">
         <v>0.0</v>
       </c>
       <c r="X70" s="247" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="Y70" s="203" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="Z70" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="AA70" s="204" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="AB70" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="AC70" s="205" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="AD70" s="204" t="n">
         <v>8417.608252999977</v>
@@ -18302,19 +18302,19 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="469" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="I79" s="463" t="n">
         <v>0.0</v>
       </c>
       <c r="J79" s="463" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="K79" s="463" t="n">
         <v>0.0</v>
       </c>
       <c r="L79" s="485" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="M79" s="463" t="n">
         <v>0.0</v>
@@ -18352,19 +18352,19 @@
         <v>0.0</v>
       </c>
       <c r="Y79" s="486" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="Z79" s="487" t="n">
         <v>0.0</v>
       </c>
       <c r="AA79" s="487" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="AB79" s="487" t="n">
         <v>0.0</v>
       </c>
       <c r="AC79" s="488" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="AD79" s="487" t="n">
         <v>0.0</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="C90" s="369" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0.0</v>
       </c>
       <c r="D90" s="368" t="n">
         <v>-1.1175870895385742e-08</v>
@@ -19981,7 +19981,7 @@
         </is>
       </c>
       <c r="T90" s="401" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0.0</v>
       </c>
       <c r="U90" s="402" t="n">
         <v>-1.1175870895385742e-08</v>
@@ -34911,19 +34911,19 @@
         </is>
       </c>
       <c r="C175" s="187" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="D175" s="179" t="n">
         <v>0.0</v>
       </c>
       <c r="E175" s="179" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="F175" s="179" t="n">
         <v>0.0</v>
       </c>
       <c r="G175" s="202" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="H175" s="187" t="n">
         <v>8417.608252999977</v>
@@ -34961,19 +34961,19 @@
         </is>
       </c>
       <c r="T175" s="203" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="U175" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="V175" s="204" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="W175" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="X175" s="205" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="Y175" s="203" t="n">
         <v>8417.608252999977</v>
@@ -39273,19 +39273,19 @@
         </is>
       </c>
       <c r="C193" s="187" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="D193" s="179" t="n">
         <v>0.0</v>
       </c>
       <c r="E193" s="179" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="F193" s="179" t="n">
         <v>0.0</v>
       </c>
       <c r="G193" s="202" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="H193" s="187" t="n">
         <v>8417.608252999977</v>
@@ -39323,19 +39323,19 @@
         </is>
       </c>
       <c r="T193" s="203" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="U193" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="V193" s="204" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="W193" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="X193" s="205" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="Y193" s="203" t="n">
         <v>8417.608252999977</v>
@@ -41645,34 +41645,34 @@
         </is>
       </c>
       <c r="C202" s="226" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="D202" s="227" t="n">
         <v>0.0</v>
       </c>
       <c r="E202" s="227" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="F202" s="227" t="n">
         <v>0.0</v>
       </c>
       <c r="G202" s="243" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="H202" s="189" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="I202" s="190" t="n">
         <v>0.0</v>
       </c>
       <c r="J202" s="190" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="K202" s="190" t="n">
         <v>0.0</v>
       </c>
       <c r="L202" s="244" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="M202" s="190" t="n">
         <v>8417.608252999977</v>
@@ -41695,34 +41695,34 @@
         </is>
       </c>
       <c r="T202" s="245" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="U202" s="246" t="n">
         <v>0.0</v>
       </c>
       <c r="V202" s="246" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="W202" s="246" t="n">
         <v>0.0</v>
       </c>
       <c r="X202" s="247" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="Y202" s="203" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="Z202" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="AA202" s="204" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0.0</v>
       </c>
       <c r="AB202" s="204" t="n">
         <v>0.0</v>
       </c>
       <c r="AC202" s="205" t="n">
-        <v>-2.7284841053187847e-12</v>
+        <v>0.0</v>
       </c>
       <c r="AD202" s="204" t="n">
         <v>8417.608252999977</v>
@@ -41745,34 +41745,34 @@
         </is>
       </c>
       <c r="AK202" s="248" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="AL202" s="249" t="n">
         <v>0.0</v>
       </c>
       <c r="AM202" s="249" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="AN202" s="249" t="n">
         <v>0.0</v>
       </c>
       <c r="AO202" s="250" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="AP202" s="220" t="n">
-        <v>-5.302677632784603e-13</v>
+        <v>0.0</v>
       </c>
       <c r="AQ202" s="209" t="n">
         <v>0.0</v>
       </c>
       <c r="AR202" s="209" t="n">
-        <v>-5.166831920410778e-13</v>
+        <v>0.0</v>
       </c>
       <c r="AS202" s="209" t="n">
         <v>0.0</v>
       </c>
       <c r="AT202" s="210" t="n">
-        <v>-3.0106402569493906e-12</v>
+        <v>0.0</v>
       </c>
       <c r="AU202" s="209" t="n">
         <v>9814.628543814859</v>
@@ -41795,34 +41795,34 @@
         </is>
       </c>
       <c r="BB202" s="251" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="BC202" s="252" t="n">
         <v>0.0</v>
       </c>
       <c r="BD202" s="252" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="BE202" s="252" t="n">
         <v>0.0</v>
       </c>
       <c r="BF202" s="253" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="BG202" s="211" t="n">
-        <v>-5.302677632784603e-13</v>
+        <v>0.0</v>
       </c>
       <c r="BH202" s="212" t="n">
         <v>0.0</v>
       </c>
       <c r="BI202" s="212" t="n">
-        <v>-5.166831920410778e-13</v>
+        <v>0.0</v>
       </c>
       <c r="BJ202" s="212" t="n">
         <v>0.0</v>
       </c>
       <c r="BK202" s="213" t="n">
-        <v>-3.0106402569493906e-12</v>
+        <v>0.0</v>
       </c>
       <c r="BL202" s="212" t="n">
         <v>9814.628543814859</v>
@@ -43602,19 +43602,19 @@
         <v>0.0</v>
       </c>
       <c r="H211" s="469" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="I211" s="463" t="n">
         <v>0.0</v>
       </c>
       <c r="J211" s="463" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="K211" s="463" t="n">
         <v>0.0</v>
       </c>
       <c r="L211" s="485" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="M211" s="463" t="n">
         <v>0.0</v>
@@ -43652,19 +43652,19 @@
         <v>0.0</v>
       </c>
       <c r="Y211" s="486" t="n">
-        <v>-5.4023344543789544e-17</v>
+        <v>0.0</v>
       </c>
       <c r="Z211" s="487" t="n">
         <v>0.0</v>
       </c>
       <c r="AA211" s="487" t="n">
-        <v>-4.238913357254197e-17</v>
+        <v>0.0</v>
       </c>
       <c r="AB211" s="487" t="n">
         <v>0.0</v>
       </c>
       <c r="AC211" s="488" t="n">
-        <v>-1.9328307062657515e-16</v>
+        <v>0.0</v>
       </c>
       <c r="AD211" s="487" t="n">
         <v>0.0</v>
@@ -45246,7 +45246,7 @@
         </is>
       </c>
       <c r="C222" s="369" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0.0</v>
       </c>
       <c r="D222" s="368" t="n">
         <v>-1.1175870895385742e-08</v>
@@ -45281,7 +45281,7 @@
         </is>
       </c>
       <c r="T222" s="401" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0.0</v>
       </c>
       <c r="U222" s="402" t="n">
         <v>-1.1175870895385742e-08</v>
@@ -48144,7 +48144,7 @@
         </is>
       </c>
       <c r="C240" s="369" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0.0</v>
       </c>
       <c r="D240" s="368" t="n">
         <v>-1.1175870895385742e-08</v>
@@ -48179,7 +48179,7 @@
         </is>
       </c>
       <c r="T240" s="401" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0.0</v>
       </c>
       <c r="U240" s="402" t="n">
         <v>-1.1175870895385742e-08</v>
